--- a/Backtest/26-10-18/NASDAQstock_26-10-18period252RS90.xlsx
+++ b/Backtest/26-10-18/NASDAQstock_26-10-18period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Backtest/26-10-18/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1DA707-F08C-2340-8A0F-319F7621CF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -205,12 +211,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -218,8 +224,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -265,17 +278,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -313,7 +334,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -347,6 +368,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -381,9 +403,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -556,9 +579,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
@@ -678,7 +701,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>95.37037037037037</v>
+        <v>95.370370370370367</v>
       </c>
       <c r="C2">
         <v>1429.5</v>
@@ -690,7 +713,7 @@
         <v>3.97</v>
       </c>
       <c r="F2">
-        <v>2.15740275073618</v>
+        <v>2.1574027507361802</v>
       </c>
       <c r="G2">
         <v>2.59</v>
@@ -702,10 +725,10 @@
         <v>43.23100051879883</v>
       </c>
       <c r="J2">
-        <v>44.29675006866455</v>
+        <v>44.296750068664551</v>
       </c>
       <c r="K2">
-        <v>46.86259971618652</v>
+        <v>46.862599716186523</v>
       </c>
       <c r="L2">
         <v>37.52089994430542</v>
@@ -780,7 +803,7 @@
         <v>57</v>
       </c>
       <c r="AK2">
-        <v>86.071592197201</v>
+        <v>86.071592197200999</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -788,7 +811,7 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>91.38176638176638</v>
+        <v>91.381766381766383</v>
       </c>
       <c r="C3">
         <v>837</v>
@@ -800,25 +823,25 @@
         <v>1.38</v>
       </c>
       <c r="F3">
-        <v>-0.4380658538322966</v>
+        <v>-0.43806585383229663</v>
       </c>
       <c r="G3">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H3">
-        <v>-0.8445394886887139</v>
+        <v>-0.84453948868871387</v>
       </c>
       <c r="I3">
-        <v>41.86084213256836</v>
+        <v>41.860842132568358</v>
       </c>
       <c r="J3">
-        <v>42.24447746276856</v>
+        <v>42.244477462768558</v>
       </c>
       <c r="K3">
-        <v>42.51787223815918</v>
+        <v>42.517872238159178</v>
       </c>
       <c r="L3">
-        <v>38.56649677276611</v>
+        <v>38.566496772766108</v>
       </c>
       <c r="M3">
         <v>0.99</v>
@@ -890,7 +913,7 @@
         <v>58</v>
       </c>
       <c r="AK3">
-        <v>84.16804128415014</v>
+        <v>84.168041284150135</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -898,7 +921,7 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>90.4320987654321</v>
+        <v>90.432098765432102</v>
       </c>
       <c r="C4">
         <v>1293</v>
@@ -910,25 +933,25 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>-0.8188681973597178</v>
+        <v>-0.81886819735971783</v>
       </c>
       <c r="G4">
         <v>1.36</v>
       </c>
       <c r="H4">
-        <v>-0.3684232668776268</v>
+        <v>-0.36842326687762678</v>
       </c>
       <c r="I4">
         <v>20.78095359802246</v>
       </c>
       <c r="J4">
-        <v>20.84652280807495</v>
+        <v>20.846522808074951</v>
       </c>
       <c r="K4">
-        <v>20.80970630645752</v>
+        <v>20.809706306457521</v>
       </c>
       <c r="L4">
-        <v>18.34767117703287</v>
+        <v>18.347671177032868</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -949,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -1008,7 +1031,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>96.34377967711301</v>
+        <v>96.343779677113005</v>
       </c>
       <c r="C5">
         <v>899</v>
@@ -1026,19 +1049,19 @@
         <v>1.57</v>
       </c>
       <c r="H5">
-        <v>0.04817842720707419</v>
+        <v>4.8178427207074187E-2</v>
       </c>
       <c r="I5">
         <v>164.2459991455078</v>
       </c>
       <c r="J5">
-        <v>157.1664985656738</v>
+        <v>157.16649856567381</v>
       </c>
       <c r="K5">
-        <v>162.1529995727539</v>
+        <v>162.15299957275391</v>
       </c>
       <c r="L5">
-        <v>144.3217495346069</v>
+        <v>144.32174953460691</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1110,7 +1133,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>21.23892711217387</v>
+        <v>21.238927112173869</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1118,7 +1141,7 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>95.32288698955365</v>
+        <v>95.322886989553652</v>
       </c>
       <c r="C6">
         <v>487</v>
@@ -1130,25 +1153,25 @@
         <v>1.77</v>
       </c>
       <c r="F6">
-        <v>-0.04724239600152198</v>
+        <v>-4.7242396001521983E-2</v>
       </c>
       <c r="G6">
         <v>1.57</v>
       </c>
       <c r="H6">
-        <v>0.04817842720707419</v>
+        <v>4.8178427207074187E-2</v>
       </c>
       <c r="I6">
-        <v>7.63674898147583</v>
+        <v>7.6367489814758303</v>
       </c>
       <c r="J6">
-        <v>7.616922330856323</v>
+        <v>7.6169223308563234</v>
       </c>
       <c r="K6">
-        <v>7.489952545166016</v>
+        <v>7.4899525451660161</v>
       </c>
       <c r="L6">
-        <v>6.350852100849152</v>
+        <v>6.3508521008491519</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -1228,7 +1251,7 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>91.88034188034187</v>
+        <v>91.880341880341874</v>
       </c>
       <c r="C7">
         <v>612</v>
@@ -1240,25 +1263,25 @@
         <v>1.31</v>
       </c>
       <c r="F7">
-        <v>-0.5082136539557688</v>
+        <v>-0.50821365395576878</v>
       </c>
       <c r="G7">
         <v>1.53</v>
       </c>
       <c r="H7">
-        <v>-0.03117427642810704</v>
+        <v>-3.117427642810704E-2</v>
       </c>
       <c r="I7">
         <v>27.19599990844727</v>
       </c>
       <c r="J7">
-        <v>27.10199995040893</v>
+        <v>27.101999950408931</v>
       </c>
       <c r="K7">
-        <v>26.90040004730225</v>
+        <v>26.900400047302249</v>
       </c>
       <c r="L7">
-        <v>24.51479999542236</v>
+        <v>24.514799995422361</v>
       </c>
       <c r="M7">
         <v>1</v>
@@ -1306,7 +1329,7 @@
         <v>17.39</v>
       </c>
       <c r="AC7">
-        <v>39.13</v>
+        <v>39.130000000000003</v>
       </c>
       <c r="AD7">
         <v>6.94</v>
@@ -1330,7 +1353,7 @@
         <v>61</v>
       </c>
       <c r="AK7">
-        <v>15.82059176267937</v>
+        <v>15.820591762679371</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1338,37 +1361,37 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>92.42640075973409</v>
+        <v>92.426400759734094</v>
       </c>
       <c r="C8">
         <v>528</v>
       </c>
       <c r="D8">
-        <v>91.04000000000001</v>
+        <v>91.04</v>
       </c>
       <c r="E8">
         <v>1.36</v>
       </c>
       <c r="F8">
-        <v>-0.4581080824390028</v>
+        <v>-0.45810808243900281</v>
       </c>
       <c r="G8">
         <v>1.08</v>
       </c>
       <c r="H8">
-        <v>-0.9238921923238951</v>
+        <v>-0.92389219232389508</v>
       </c>
       <c r="I8">
-        <v>90.6082260131836</v>
+        <v>90.608226013183597</v>
       </c>
       <c r="J8">
-        <v>90.51834030151367</v>
+        <v>90.518340301513675</v>
       </c>
       <c r="K8">
-        <v>90.52529205322266</v>
+        <v>90.525292053222657</v>
       </c>
       <c r="L8">
-        <v>80.22835052490234</v>
+        <v>80.228350524902339</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -1413,7 +1436,7 @@
         <v>14.69</v>
       </c>
       <c r="AB8">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AC8">
         <v>45.83</v>
@@ -1444,6 +1467,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>